--- a/artfynd/A 60541-2022 artfynd.xlsx
+++ b/artfynd/A 60541-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125072532</v>
+        <v>125073870</v>
       </c>
       <c r="B2" t="n">
-        <v>57454</v>
+        <v>56725</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102622</v>
+        <v>102613</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pärluggla</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Aegolius funereus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -761,12 +761,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125073870</v>
+        <v>125072532</v>
       </c>
       <c r="B3" t="n">
-        <v>56725</v>
+        <v>57454</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,16 +809,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102613</v>
+        <v>102622</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Pärluggla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Aegolius funereus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 60541-2022 artfynd.xlsx
+++ b/artfynd/A 60541-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125073870</v>
+        <v>125072532</v>
       </c>
       <c r="B2" t="n">
-        <v>56725</v>
+        <v>57454</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102613</v>
+        <v>102622</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Pärluggla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Aegolius funereus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -761,12 +761,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125072532</v>
+        <v>125073870</v>
       </c>
       <c r="B3" t="n">
-        <v>57454</v>
+        <v>56725</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,16 +809,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102622</v>
+        <v>102613</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pärluggla</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Aegolius funereus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 60541-2022 artfynd.xlsx
+++ b/artfynd/A 60541-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125073870</v>
       </c>
       <c r="B2" t="n">
-        <v>56725</v>
+        <v>56839</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>125072532</v>
       </c>
       <c r="B3" t="n">
-        <v>57454</v>
+        <v>57471</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 60541-2022 artfynd.xlsx
+++ b/artfynd/A 60541-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125073870</v>
+        <v>125072532</v>
       </c>
       <c r="B2" t="n">
-        <v>56839</v>
+        <v>57471</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102613</v>
+        <v>102622</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Pärluggla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Aegolius funereus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -761,12 +761,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125072532</v>
+        <v>125073870</v>
       </c>
       <c r="B3" t="n">
-        <v>57471</v>
+        <v>56839</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,16 +809,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102622</v>
+        <v>102613</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pärluggla</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Aegolius funereus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 60541-2022 artfynd.xlsx
+++ b/artfynd/A 60541-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125072532</v>
       </c>
       <c r="B2" t="n">
-        <v>57716</v>
+        <v>57718</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 60541-2022 artfynd.xlsx
+++ b/artfynd/A 60541-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125072532</v>
+        <v>125073870</v>
       </c>
       <c r="B2" t="n">
-        <v>57718</v>
+        <v>57144</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102622</v>
+        <v>102613</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pärluggla</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Aegolius funereus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -756,12 +756,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,27 +788,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125073870</v>
+        <v>125072532</v>
       </c>
       <c r="B3" t="n">
-        <v>56846</v>
+        <v>57785</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102613</v>
+        <v>102622</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Pärluggla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Aegolius funereus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 60541-2022 artfynd.xlsx
+++ b/artfynd/A 60541-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -785,6 +790,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125073870</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,8 +908,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125072532</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>